--- a/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,9 +501,14 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45462.85416666666</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">szpala l 
+  usa </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">saputo stadium
@@ -553,9 +558,14 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45462.85416666666</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">bank of america stadium
@@ -605,9 +615,14 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45462.85416666666</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">audi field
@@ -657,9 +672,14 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45462.85416666666</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">chase stadium
@@ -709,9 +729,14 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45462.85416666666</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">bmo field
@@ -761,9 +786,14 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45462.86458333334</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>45462.98958333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">tql stadium
@@ -813,9 +843,14 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45462.89583333334</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">q2 stadium
@@ -865,9 +900,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45462.89583333334</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">toyota stadium
@@ -917,9 +957,14 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45462.89583333334</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">shell energy stadium
@@ -969,9 +1014,14 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45462.89583333334</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">children s mercy park
@@ -1021,9 +1071,14 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45462.89583333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">citypark
@@ -1063,6 +1118,120 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45463.10416666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>167</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45463.10416666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>167</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>2024</v>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,45 +497,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hK8xvrmh</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
+          <t xml:space="preserve">de oliveira m 
   usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23112</v>
+        <v>20371</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -554,45 +554,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rwisKhLu</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">chapman a 
+          <t xml:space="preserve">ford t 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bank of america stadium
-  charlotte  nc </t>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>74500</v>
+        <v>20000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>O6hjfSXE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -611,45 +611,40 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2u7rIWkh</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45462.97916666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
-        </is>
-      </c>
+        <v>45465.85416666666</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20000</v>
+        <v>26000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -668,570 +663,627 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tW5nHj5b</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>167</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WYwYSm4A</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45465.85416666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simon n 
+  usa </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>25500</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>167</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>APxxS7JG</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45465.85416666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">da silva a 
+  usa </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>167</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>4nxtRRYM</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45465.89583333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>19400</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>167</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>IktpQolT</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45465.89583333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>167</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>OWICL5dp</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45465.89583333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>22423</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>167</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Sx1kytXA</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45465.9375</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>167</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2NHGKPBj</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45465.9375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>167</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>UT5bq9li</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">boiko s 
   ukr </t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chase stadium
-  fort lauderdale  fl </t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>21550</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0AheRyBg</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>inter miami</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>columbus crew</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>167</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WA7tw22b</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45462.97916666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">penso c 
-  usa </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bmo field
-  toronto  on </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>30991</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>toronto fc</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>84yIDQMe</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>nashville sc</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>167</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>MTkoJCzn</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45462.98958333334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>26000</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>8btog05R</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>fc cincinnati</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Szrwix67</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>philadelphia union</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>167</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>zg5jGAK4</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45463.02083333334</v>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>167</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Ma0gz0nH</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">unkel t 
   usa </t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">q2 stadium
-  austin  tx </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>20700</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>IeT6JBE3</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>austin fc</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>los angeles fc</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>167</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>ld9fFUZA</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45463.02083333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">demianchuk s 
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">providence park
+  portland  or </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>25218</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>167</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badawi m 
   usa </t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">toyota stadium
-  frisco  tx </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>20500</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>4GtbI4Q1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>fc dallas</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>zXFxsw2a</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>minnesota united</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>167</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WKbaElkH</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45463.02083333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>22039</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>houston dynamo</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>seattle sounders</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>167</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>ABc3D84N</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45463.02083333334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allatin m 
-  usa </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">children s mercy park
-  kansas city  mo </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>18500</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>sporting kansas city</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>real salt lake</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>167</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vo27CSJT</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45463.02083333334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gonzales g 
-  usa </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>22423</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>4r4sKQud</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>st  louis city</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>colorado rapids</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>167</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>tflZ7nSp</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45463.10416666666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vazquez r 
-  usa </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dignity health sports park
-  carson  ca </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>27000</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>U3ebh62R</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>los angeles galaxy</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>vZraQYnO</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>new york city</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>167</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>raSHWV4o</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45463.10416666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">de oliveira m 
-  usa </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">paypal park
-  san jose  ca </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>18000</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>x05z14ue</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>san jose earthquakes</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>portland timbers</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>167</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="J15" t="n">
+        <v>167</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>2024</v>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45466.0625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45466.0625</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1287,6 +1287,1410 @@
         <v>2024</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45471.97916666666</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>54251</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>167</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>167</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>167</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>167</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>167</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>167</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>167</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>167</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>167</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>167</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">providence park
+  portland  or </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>25218</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>167</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>167</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>167</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>54405</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>167</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>167</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>74500</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>167</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>167</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>54251</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>167</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>30991</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>167</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45476.98958333334</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>167</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>61500</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>167</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>19400</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>167</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>22423</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>167</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45477.0625</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>167</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45478.02083333334</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>167</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45478.0625</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>167</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45478.10416666666</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>167</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2024</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45465.9375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45465.9375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,20 +475,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
@@ -501,7 +521,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -538,16 +558,36 @@
           <t>sporting kansas city</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>nancy wilfried</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>vermes peter</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>167</v>
       </c>
-      <c r="K2" t="n">
+      <c r="O2" t="n">
         <v>1671</v>
       </c>
-      <c r="L2" t="n">
+      <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="n">
+      <c r="Q2" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -558,7 +598,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -595,16 +635,36 @@
           <t>houston dynamo</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>lesesne troy</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>olsen ben</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
         <v>167</v>
       </c>
-      <c r="K3" t="n">
+      <c r="O3" t="n">
         <v>1671</v>
       </c>
-      <c r="L3" t="n">
+      <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="n">
+      <c r="Q3" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -615,9 +675,14 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.85416666666</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">tql stadium
@@ -647,16 +712,36 @@
           <t>new england revolution</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>noonan pat</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>porter caleb</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
         <v>167</v>
       </c>
-      <c r="K4" t="n">
+      <c r="O4" t="n">
         <v>1671</v>
       </c>
-      <c r="L4" t="n">
+      <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -667,7 +752,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -704,16 +789,36 @@
           <t>toronto fc</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>schwarz sandro</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>herdman john</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
         <v>167</v>
       </c>
-      <c r="K5" t="n">
+      <c r="O5" t="n">
         <v>1671</v>
       </c>
-      <c r="L5" t="n">
+      <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -724,7 +829,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -761,16 +866,36 @@
           <t>chicago fire</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>pareja oscar</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>klopas frank</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
         <v>167</v>
       </c>
-      <c r="K6" t="n">
+      <c r="O6" t="n">
         <v>1671</v>
       </c>
-      <c r="L6" t="n">
+      <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="n">
+      <c r="Q6" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -781,7 +906,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -818,16 +943,36 @@
           <t>charlotte</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>curtin jim</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>smith dean</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
         <v>167</v>
       </c>
-      <c r="K7" t="n">
+      <c r="O7" t="n">
         <v>1671</v>
       </c>
-      <c r="L7" t="n">
+      <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
+      <c r="Q7" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -838,7 +983,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -875,16 +1020,20 @@
           <t>austin fc</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
         <v>167</v>
       </c>
-      <c r="K8" t="n">
+      <c r="O8" t="n">
         <v>1671</v>
       </c>
-      <c r="L8" t="n">
+      <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -895,7 +1044,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -932,16 +1081,20 @@
           <t>new york city</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
         <v>167</v>
       </c>
-      <c r="K9" t="n">
+      <c r="O9" t="n">
         <v>1671</v>
       </c>
-      <c r="L9" t="n">
+      <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" t="n">
+      <c r="Q9" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -952,7 +1105,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -989,301 +1142,20 @@
           <t>atlanta utd</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
         <v>167</v>
       </c>
-      <c r="K10" t="n">
+      <c r="O10" t="n">
         <v>1671</v>
       </c>
-      <c r="L10" t="n">
+      <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="M10" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Sx1kytXA</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45465.9375</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dick s sporting goods park
-  commerce city  co </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>18061</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>colorado rapids</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>cf montreal</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>167</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2NHGKPBj</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45465.9375</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">america first field
-  sandy  ut </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>20213</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>real salt lake</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>U3ebh62R</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>los angeles galaxy</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>167</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>UT5bq9li</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bmo stadium
-  los angeles  ca </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>22000</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>los angeles fc</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>x05z14ue</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>san jose earthquakes</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>167</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ma0gz0nH</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">providence park
-  portland  or </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>25218</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>portland timbers</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>vancouver whitecaps</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>167</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>8K42rT3c</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badawi m 
-  usa </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>seattle sounders</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>fc dallas</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>167</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="Q10" t="n">
         <v>2024</v>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,40 +475,20 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>id_country</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>coach_home</t>
+          <t>id_competition</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_country</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
@@ -517,645 +497,171 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">lower com field
-  columbus  oh </t>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>20371</v>
+        <v>22000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>zoZ995af</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>nancy wilfried</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>jBBpU7Y0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>vermes peter</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>167</v>
       </c>
-      <c r="O2" t="n">
+      <c r="K2" t="n">
         <v>1671</v>
       </c>
-      <c r="P2" t="n">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="M2" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ford t 
+          <t xml:space="preserve">unkel t 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">providence park
+  portland  or </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20000</v>
+        <v>25218</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>nJ01AhXP</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>lesesne troy</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>86yPt28f</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>olsen ben</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>167</v>
       </c>
-      <c r="O3" t="n">
+      <c r="K3" t="n">
         <v>1671</v>
       </c>
-      <c r="P3" t="n">
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="M3" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>8K42rT3c</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">freemon j 
+          <t xml:space="preserve">badawi m 
   usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26000</v>
+        <v>72000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>new england revolution</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>roEEsq76</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>noonan pat</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>GzULyFoh</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>porter caleb</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>167</v>
       </c>
-      <c r="O4" t="n">
+      <c r="K4" t="n">
         <v>1671</v>
       </c>
-      <c r="P4" t="n">
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>ln2oxMH4</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">red bull arena
-  harrison  nj </t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>25000</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>zV5YmQAr</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>new york red bulls</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>toronto fc</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>rJ9D8rzj</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>schwarz sandro</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>xA45kovo</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>herdman john</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>167</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1671</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WYwYSm4A</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simon n 
-  usa </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inter co stadium
-  orlando  fl </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>25500</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>orlando city</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>UwAwNo2E</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>chicago fire</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>K4zRMgTN</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>pareja oscar</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Uw6sTk0t</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>klopas frank</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>167</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1671</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>APxxS7JG</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">da silva a 
-  usa </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">subaru park
-  chester  pa </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>18500</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Szrwix67</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>philadelphia union</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>QJF7WTFB</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>charlotte</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>6BusaLE3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>curtin jim</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>022mBmSn</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>smith dean</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>167</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1671</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>4nxtRRYM</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45466.02083333334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz field
-  saint paul  mn </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>19400</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>zXFxsw2a</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>minnesota united</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>IeT6JBE3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>austin fc</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>167</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1671</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>IktpQolT</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45466.02083333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rivas v 
-  usa </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">geodis park
-  nashville  tn </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>84yIDQMe</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>nashville sc</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>vZraQYnO</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>new york city</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>167</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1671</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>OWICL5dp</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45466.02083333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>22423</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>4r4sKQud</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>st  louis city</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>EPngUvhk</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>atlanta utd</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>167</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1671</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M4" t="n">
         <v>2024</v>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,20 +475,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
@@ -538,16 +558,36 @@
           <t>san jose earthquakes</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>cherundolo steve</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gonzalez luchi</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>167</v>
       </c>
-      <c r="K2" t="n">
+      <c r="O2" t="n">
         <v>1671</v>
       </c>
-      <c r="L2" t="n">
+      <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="n">
+      <c r="Q2" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -595,16 +635,36 @@
           <t>vancouver whitecaps</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>neville phil</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>sartini vanni</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
         <v>167</v>
       </c>
-      <c r="K3" t="n">
+      <c r="O3" t="n">
         <v>1671</v>
       </c>
-      <c r="L3" t="n">
+      <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="n">
+      <c r="Q3" t="n">
         <v>2024</v>
       </c>
     </row>
@@ -652,16 +712,36 @@
           <t>fc dallas</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>schmetzer brian</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>luccin peter</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
         <v>167</v>
       </c>
-      <c r="K4" t="n">
+      <c r="O4" t="n">
         <v>1671</v>
       </c>
-      <c r="L4" t="n">
+      <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
         <v>2024</v>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,40 +475,20 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>id_country</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>coach_home</t>
+          <t>id_competition</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_country</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
@@ -517,231 +497,2132 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45466.10416666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
+        <v>45471.97916666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>54251</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>167</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>167</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>167</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>167</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>167</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>167</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>167</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>167</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>167</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">bmo stadium
   los angeles  ca </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E11" t="n">
         <v>22000</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>txUJt9AR</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>los angeles fc</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>x05z14ue</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>san jose earthquakes</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>UL7r7duf</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>cherundolo steve</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Onn3tCA5</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gonzalez luchi</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>167</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1671</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Ma0gz0nH</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45466.10416666666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>167</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">providence park
   portland  or </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E12" t="n">
         <v>25218</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>bm8usLzB</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>portland timbers</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>vancouver whitecaps</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>EqKWmJfM</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>neville phil</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Sd7snoa0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>sartini vanni</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>167</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1671</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>8K42rT3c</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45466.10416666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badawi m 
-  usa </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>167</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>167</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">lumen field
   seattle  wa </t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E14" t="n">
         <v>72000</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>6P5S63Ah</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>seattle sounders</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>167</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>54405</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>167</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>167</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>74500</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>167</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>167</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>54251</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>167</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>30991</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>167</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45476.98958333334</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>167</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>61500</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>167</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>19400</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>167</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>22423</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>167</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45477.0625</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>167</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45478.02083333334</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>4GtbI4Q1</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>fc dallas</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>tOpyQa24</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>schmetzer brian</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>WWvwigh8</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>luccin peter</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>167</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1671</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>167</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45478.0625</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>167</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45478.10416666666</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>167</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>167</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>167</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>167</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>25500</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>167</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>167</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45480.02083333334</v>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>20700</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>167</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45480.0625</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>167</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45480.10416666666</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>167</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45481.02083333334</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>167</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45481.02083333334</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>167</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45481.0625</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>167</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45481.10416666666</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>167</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45481.10416666666</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">providence park
+  portland  or </t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>25218</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>167</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45481.83333333334</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>167</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
         <v>2024</v>
       </c>
     </row>

--- a/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,49 +493,54 @@
           <t>season</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.85416666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">de oliveira m 
-  usa </t>
-        </is>
-      </c>
+        <v>45471.85416666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">lower com field
-  columbus  oh </t>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>20371</v>
+        <v>54251</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -550,49 +555,54 @@
       <c r="M2" t="n">
         <v>2024</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.85416666666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ford t 
-  usa </t>
-        </is>
-      </c>
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20000</v>
+        <v>71000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -607,44 +617,54 @@
       <c r="M3" t="n">
         <v>2024</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26000</v>
+        <v>23112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -659,106 +679,116 @@
       <c r="M4" t="n">
         <v>2024</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.85416666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
-        </is>
-      </c>
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>167</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45472.85416666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">red bull arena
   harrison  nj </t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E6" t="n">
         <v>25000</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>zV5YmQAr</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>new york red bulls</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>toronto fc</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>167</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WYwYSm4A</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45465.85416666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">simon n 
-  usa </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inter co stadium
-  orlando  fl </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>25500</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>orlando city</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>O6hjfSXE</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -773,49 +803,54 @@
       <c r="M6" t="n">
         <v>2024</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.85416666666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">da silva a 
-  usa </t>
-        </is>
-      </c>
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">subaru park
-  chester  pa </t>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18500</v>
+        <v>20500</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -830,49 +865,54 @@
       <c r="M7" t="n">
         <v>2024</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45465.89583333334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
-        </is>
-      </c>
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz field
-  saint paul  mn </t>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>19400</v>
+        <v>22039</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -887,22 +927,27 @@
       <c r="M8" t="n">
         <v>2024</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45465.89583333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rivas v 
-  usa </t>
-        </is>
-      </c>
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">geodis park
@@ -924,12 +969,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -944,49 +989,54 @@
       <c r="M9" t="n">
         <v>2024</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45465.89583333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
-        </is>
-      </c>
+        <v>45472.89583333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22423</v>
+        <v>18500</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1001,49 +1051,54 @@
       <c r="M10" t="n">
         <v>2024</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45465.9375</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
-        </is>
-      </c>
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">dick s sporting goods park
-  commerce city  co </t>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18061</v>
+        <v>22000</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>jmBZNRn8</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>colorado rapids</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>cf montreal</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1058,49 +1113,54 @@
       <c r="M11" t="n">
         <v>2024</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45465.9375</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
-        </is>
-      </c>
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">america first field
-  sandy  ut </t>
+          <t xml:space="preserve">providence park
+  portland  or </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20213</v>
+        <v>25218</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1115,49 +1175,54 @@
       <c r="M12" t="n">
         <v>2024</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo stadium
-  los angeles  ca </t>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>22000</v>
+        <v>18000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1172,49 +1237,54 @@
       <c r="M13" t="n">
         <v>2024</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
-        </is>
-      </c>
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">providence park
-  portland  or </t>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25218</v>
+        <v>72000</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1229,49 +1299,54 @@
       <c r="M14" t="n">
         <v>2024</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badawi m 
-  usa </t>
-        </is>
-      </c>
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>72000</v>
+        <v>54405</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>6P5S63Ah</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1285,6 +1360,16 @@
       </c>
       <c r="M15" t="n">
         <v>2024</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1372,6 +1372,1928 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45476.8125</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>167</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>74500</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>167</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>167</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>54251</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>167</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>30991</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>167</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45476.86458333334</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>68756</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>167</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>61500</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>167</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>19400</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>167</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>22423</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>167</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>167</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45477.89583333334</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>167</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45477.9375</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>167</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45477.97916666666</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>167</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>167</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>20371</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>167</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>167</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>25500</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>167</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>167</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45479.89583333334</v>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>20700</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>167</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45479.9375</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>167</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>167</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45480.89583333334</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>167</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45480.89583333334</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>167</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45480.89583333334</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>167</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45480.9375</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>167</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45480.97916666666</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>167</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45480.97916666666</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">providence park
+  portland  or </t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>25218</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>167</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>SKZvN7pn</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45482.83333333334</v>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>dtMNCXyk</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>indy eleven</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>167</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1672</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>APpAklQ6</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45483</v>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heart health park
+  sacramento  ca </t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>11569</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>z3BFwb83</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>sacramento republic</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>167</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1672</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>d0ReJPqB</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>45483.91666666666</v>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>167</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1672</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>0YXnLoFb</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45484</v>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo stadium
+  los angeles  ca </t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>dI5p0xzH</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>new mexico</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>167</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1672</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -513,7 +513,12 @@
       <c r="B2" s="2" t="n">
         <v>45471.85416666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">yankee stadium
@@ -575,7 +580,12 @@
       <c r="B3" s="2" t="n">
         <v>45472.85416666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">mercedes benz stadium
@@ -637,7 +647,12 @@
       <c r="B4" s="2" t="n">
         <v>45472.85416666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">saputo stadium
@@ -699,7 +714,12 @@
       <c r="B5" s="2" t="n">
         <v>45472.85416666666</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fierro r 
+  usa </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">gillette stadium
@@ -761,7 +781,12 @@
       <c r="B6" s="2" t="n">
         <v>45472.85416666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badawi m 
+  usa </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">red bull arena
@@ -823,7 +848,12 @@
       <c r="B7" s="2" t="n">
         <v>45472.89583333334</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rivas v 
+  usa </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">toyota stadium
@@ -885,7 +915,12 @@
       <c r="B8" s="2" t="n">
         <v>45472.89583333334</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lauziere p 
+  can </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">shell energy stadium
@@ -947,7 +982,12 @@
       <c r="B9" s="2" t="n">
         <v>45472.89583333334</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">szpala l 
+  usa </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">geodis park
@@ -1009,7 +1049,12 @@
       <c r="B10" s="2" t="n">
         <v>45472.89583333334</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">children s mercy park
@@ -1071,7 +1116,12 @@
       <c r="B11" s="2" t="n">
         <v>45472.97916666666</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">bmo stadium
@@ -1133,7 +1183,12 @@
       <c r="B12" s="2" t="n">
         <v>45472.97916666666</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">providence park
@@ -1195,7 +1250,12 @@
       <c r="B13" s="2" t="n">
         <v>45472.97916666666</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">paypal park
@@ -1257,7 +1317,12 @@
       <c r="B14" s="2" t="n">
         <v>45472.97916666666</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">lumen field
@@ -1319,7 +1384,12 @@
       <c r="B15" s="2" t="n">
         <v>45472.97916666666</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t xml:space="preserve">bc place

--- a/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -507,112 +507,102 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GvBXzXxS</t>
+          <t>AszX60rp</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45486.85416666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>167</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>jix3jCxF</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">saputo stadium
   montreal  qc </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>23112</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>j9cigLCr</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>cf montreal</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>EPngUvhk</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>atlanta utd</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>167</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>QHhnaCp6</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45486.85416666666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>O6hjfSXE</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>dc united</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +631,40 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Iigr0hVa</t>
+          <t>h6Py6Kcj</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45486.85416666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gonzales g 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">chase stadium
+  fort lauderdale  fl </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26000</v>
+        <v>21550</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,18 +693,13 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>48ijbWaC</t>
+          <t>WdOu5vDd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45486.85416666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">gillette stadium
@@ -741,12 +721,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -775,45 +755,40 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dYh0Wjoq</t>
+          <t>KCHNTNkc</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45486.85416666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chapman a 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo field
-  toronto  on </t>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>30991</v>
+        <v>25000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -842,179 +817,164 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>nXtecjFI</t>
+          <t>b3GRSs53</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45486.89583333334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>25500</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>167</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>tS5WR1K9</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45493.85416666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subaru park
+  chester  pa </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>167</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h29zRLZF</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45493.89583333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">q2 stadium
   austin  tx </t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>20700</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E9" t="n">
+        <v>20738</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>IeT6JBE3</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>austin fc</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>seattle sounders</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>167</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>0zoadAUO</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45486.89583333334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">soldier field
-  chicago  il </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>61500</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>UwAwNo2E</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>chicago fire</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>vZraQYnO</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>new york city</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>167</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>EwZtLg7P</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45486.89583333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">touchan r 
-  usa </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">toyota stadium
-  frisco  tx </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>20500</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>fc dallas</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1043,45 +1003,40 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GnL8GDFt</t>
+          <t>QF7rPa4S</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45486.89583333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">freemon j 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.89583333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22039</v>
+        <v>19400</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1110,45 +1065,40 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>zPi4VA0k</t>
+          <t>nP8vQukM</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45486.89583333334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
-        </is>
-      </c>
+        <v>45493.89583333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22423</v>
+        <v>21650</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>4r4sKQud</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>st  louis city</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1177,18 +1127,13 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>YNFDFXUn</t>
+          <t>69kBKJCq</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45486.9375</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ford t 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.9375</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">dick s sporting goods park
@@ -1210,12 +1155,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1244,45 +1189,40 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>6yELDBaa</t>
+          <t>vNmJIcsd</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45486.97569444445</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.97916666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">providence park
-  portland  or </t>
+          <t xml:space="preserve">lumen field
+  seattle  wa </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>25218</v>
+        <v>72000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>bm8usLzB</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1311,45 +1251,40 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>CEEHEipg</t>
+          <t>MHXbihN8</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45486.97916666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">szpala l 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.97916666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo stadium
-  los angeles  ca </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>22000</v>
+        <v>54405</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1378,45 +1313,40 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>4MWOCVE5</t>
+          <t>p0lFJwSk</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45486.97916666666</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">da silva a 
-  usa </t>
-        </is>
-      </c>
+        <v>45493.98958333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">paypal park
-  san jose  ca </t>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>18000</v>
+        <v>27000</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="J15" t="n">

--- a/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/usa/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,30 +475,50 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
         </is>
@@ -513,7 +533,12 @@
       <c r="B2" s="2" t="n">
         <v>45493.85416666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">mercedes benz stadium
@@ -543,24 +568,44 @@
           <t>columbus crew</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>valentino rob</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>nancy wilfried</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>167</v>
       </c>
-      <c r="K2" t="n">
+      <c r="O2" t="n">
         <v>1671</v>
       </c>
-      <c r="L2" t="n">
+      <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="n">
+      <c r="Q2" t="n">
         <v>2024</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -575,7 +620,12 @@
       <c r="B3" s="2" t="n">
         <v>45493.85416666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villarreal a 
+  usa </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">saputo stadium
@@ -605,24 +655,44 @@
           <t>toronto fc</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>courtois laurent</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>herdman john</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
         <v>167</v>
       </c>
-      <c r="K3" t="n">
+      <c r="O3" t="n">
         <v>1671</v>
       </c>
-      <c r="L3" t="n">
+      <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="n">
+      <c r="Q3" t="n">
         <v>2024</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -637,7 +707,12 @@
       <c r="B4" s="2" t="n">
         <v>45493.85416666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">chase stadium
@@ -667,24 +742,44 @@
           <t>chicago fire</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>martino gerardo</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>klopas frank</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
         <v>167</v>
       </c>
-      <c r="K4" t="n">
+      <c r="O4" t="n">
         <v>1671</v>
       </c>
-      <c r="L4" t="n">
+      <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
         <v>2024</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -699,7 +794,12 @@
       <c r="B5" s="2" t="n">
         <v>45493.85416666666</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">gillette stadium
@@ -729,24 +829,44 @@
           <t>fc dallas</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>porter caleb</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>luccin peter</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
         <v>167</v>
       </c>
-      <c r="K5" t="n">
+      <c r="O5" t="n">
         <v>1671</v>
       </c>
-      <c r="L5" t="n">
+      <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
         <v>2024</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -761,7 +881,12 @@
       <c r="B6" s="2" t="n">
         <v>45493.85416666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">red bull arena
@@ -791,24 +916,44 @@
           <t>fc cincinnati</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>schwarz sandro</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>noonan pat</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
         <v>167</v>
       </c>
-      <c r="K6" t="n">
+      <c r="O6" t="n">
         <v>1671</v>
       </c>
-      <c r="L6" t="n">
+      <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="n">
+      <c r="Q6" t="n">
         <v>2024</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -823,7 +968,12 @@
       <c r="B7" s="2" t="n">
         <v>45493.85416666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">inter co stadium
@@ -853,24 +1003,44 @@
           <t>new york city</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>pareja oscar</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>cushing nicholas</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
         <v>167</v>
       </c>
-      <c r="K7" t="n">
+      <c r="O7" t="n">
         <v>1671</v>
       </c>
-      <c r="L7" t="n">
+      <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
+      <c r="Q7" t="n">
         <v>2024</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -885,7 +1055,12 @@
       <c r="B8" s="2" t="n">
         <v>45493.85416666666</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">subaru park
@@ -915,24 +1090,44 @@
           <t>nashville sc</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>curtin jim</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>63fk89be</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>callaghan brian</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
         <v>167</v>
       </c>
-      <c r="K8" t="n">
+      <c r="O8" t="n">
         <v>1671</v>
       </c>
-      <c r="L8" t="n">
+      <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
         <v>2024</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -947,7 +1142,12 @@
       <c r="B9" s="2" t="n">
         <v>45493.89583333334</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">q2 stadium
@@ -977,24 +1177,28 @@
           <t>charlotte</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
         <v>167</v>
       </c>
-      <c r="K9" t="n">
+      <c r="O9" t="n">
         <v>1671</v>
       </c>
-      <c r="L9" t="n">
+      <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" t="n">
+      <c r="Q9" t="n">
         <v>2024</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -1009,7 +1213,12 @@
       <c r="B10" s="2" t="n">
         <v>45493.89583333334</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pekmic i 
+  usa </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">allianz field
@@ -1039,24 +1248,28 @@
           <t>san jose earthquakes</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
         <v>167</v>
       </c>
-      <c r="K10" t="n">
+      <c r="O10" t="n">
         <v>1671</v>
       </c>
-      <c r="L10" t="n">
+      <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="M10" t="n">
+      <c r="Q10" t="n">
         <v>2024</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -1071,7 +1284,12 @@
       <c r="B11" s="2" t="n">
         <v>45493.89583333334</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">children s mercy park
@@ -1101,24 +1319,28 @@
           <t>st  louis city</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
         <v>167</v>
       </c>
-      <c r="K11" t="n">
+      <c r="O11" t="n">
         <v>1671</v>
       </c>
-      <c r="L11" t="n">
+      <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="M11" t="n">
+      <c r="Q11" t="n">
         <v>2024</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -1133,7 +1355,12 @@
       <c r="B12" s="2" t="n">
         <v>45493.9375</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">touchan r 
+  usa </t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">dick s sporting goods park
@@ -1163,24 +1390,28 @@
           <t>real salt lake</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
         <v>167</v>
       </c>
-      <c r="K12" t="n">
+      <c r="O12" t="n">
         <v>1671</v>
       </c>
-      <c r="L12" t="n">
+      <c r="P12" t="n">
         <v>0</v>
       </c>
-      <c r="M12" t="n">
+      <c r="Q12" t="n">
         <v>2024</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -1195,7 +1426,12 @@
       <c r="B13" s="2" t="n">
         <v>45493.97916666666</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">lumen field
@@ -1225,24 +1461,28 @@
           <t>los angeles fc</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
         <v>167</v>
       </c>
-      <c r="K13" t="n">
+      <c r="O13" t="n">
         <v>1671</v>
       </c>
-      <c r="L13" t="n">
+      <c r="P13" t="n">
         <v>0</v>
       </c>
-      <c r="M13" t="n">
+      <c r="Q13" t="n">
         <v>2024</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -1257,7 +1497,12 @@
       <c r="B14" s="2" t="n">
         <v>45493.97916666666</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bazakos f 
+  usa </t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">bc place
@@ -1287,24 +1532,28 @@
           <t>houston dynamo</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
         <v>167</v>
       </c>
-      <c r="K14" t="n">
+      <c r="O14" t="n">
         <v>1671</v>
       </c>
-      <c r="L14" t="n">
+      <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="M14" t="n">
+      <c r="Q14" t="n">
         <v>2024</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -1319,7 +1568,12 @@
       <c r="B15" s="2" t="n">
         <v>45493.98958333334</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t xml:space="preserve">dignity health sports park
@@ -1349,24 +1603,28 @@
           <t>portland timbers</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
         <v>167</v>
       </c>
-      <c r="K15" t="n">
+      <c r="O15" t="n">
         <v>1671</v>
       </c>
-      <c r="L15" t="n">
+      <c r="P15" t="n">
         <v>0</v>
       </c>
-      <c r="M15" t="n">
+      <c r="Q15" t="n">
         <v>2024</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
